--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmunip.CAMPUS\source\repos\ABM-Random-Forest\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmunip.CAMPUS\source\repos\ABM-NM-optimization\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{504325C3-5D65-446C-B0DF-D439C97FDFA7}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C141CB2-284A-4BA7-9291-C48AA37AE700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="4560" yWindow="2310" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="6075" yWindow="2325" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -35,7 +35,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="113" uniqueCount="82">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="111" uniqueCount="81">
   <si>
     <t>Mean</t>
   </si>
@@ -232,55 +232,52 @@
     <t>biomaterial:elastic_modulus:intercept</t>
   </si>
   <si>
-    <t>biomaterial:elastic_modulus:alginate_concentration</t>
-  </si>
-  <si>
     <t>biomaterial:elastic_modulus:crosslinker_density</t>
   </si>
   <si>
+    <t>biomaterial:pore_size:crosslinker_effect</t>
+  </si>
+  <si>
+    <t>biomaterial:pore_size:baseline</t>
+  </si>
+  <si>
+    <t>biomaterial:mass_loss:baseline</t>
+  </si>
+  <si>
+    <t>biomaterial:mass_loss:crosslinker_effect</t>
+  </si>
+  <si>
+    <t>biomaterial:mass_loss:time_effect</t>
+  </si>
+  <si>
+    <t>biomaterial:mass_loss:crosslinker_time_interaction</t>
+  </si>
+  <si>
+    <t>biomaterial:swell_ratio:baseline</t>
+  </si>
+  <si>
+    <t>biomaterial:swell_ratio:time_effect</t>
+  </si>
+  <si>
+    <t>biomaterial:swell_ratio:alginate_concentration_effect</t>
+  </si>
+  <si>
+    <t>biomaterial:swell_ratio:time_crosslinker_interaction</t>
+  </si>
+  <si>
+    <t>biomaterial:swell_ratio:alginate_crosslinker_interaction</t>
+  </si>
+  <si>
     <t>biomaterial:elastic_modulus:alginate_molecular_weight</t>
   </si>
   <si>
-    <t>biomaterial:elastic_modulus:alginate_crosslinker_interaction</t>
-  </si>
-  <si>
-    <t>biomaterial:elastic_modulus:alginate_mw_interaction</t>
-  </si>
-  <si>
-    <t>biomaterial:elastic_modulus:mw_crosslinker_interaction</t>
-  </si>
-  <si>
-    <t>biomaterial:pore_size:crosslinker_effect</t>
-  </si>
-  <si>
-    <t>biomaterial:pore_size:baseline</t>
-  </si>
-  <si>
-    <t>biomaterial:mass_loss:baseline</t>
-  </si>
-  <si>
-    <t>biomaterial:mass_loss:crosslinker_effect</t>
-  </si>
-  <si>
-    <t>biomaterial:mass_loss:time_effect</t>
-  </si>
-  <si>
-    <t>biomaterial:mass_loss:crosslinker_time_interaction</t>
-  </si>
-  <si>
-    <t>biomaterial:swell_ratio:baseline</t>
-  </si>
-  <si>
-    <t>biomaterial:swell_ratio:time_effect</t>
-  </si>
-  <si>
-    <t>biomaterial:swell_ratio:alginate_concentration_effect</t>
-  </si>
-  <si>
-    <t>biomaterial:swell_ratio:time_crosslinker_interaction</t>
-  </si>
-  <si>
-    <t>biomaterial:swell_ratio:alginate_crosslinker_interaction</t>
+    <t>stem:proliferation:static_probability</t>
+  </si>
+  <si>
+    <t>stem:differentiation:static_probability</t>
+  </si>
+  <si>
+    <t>progen:differentiation:static_probability</t>
   </si>
 </sst>
 </file>
@@ -328,11 +325,12 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="4">
+  <cellXfs count="5">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -647,7 +645,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:K68"/>
+  <dimension ref="A1:K67"/>
   <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="2" width="21" customWidth="1"/>
@@ -722,7 +720,7 @@
         <v>10</v>
       </c>
       <c r="D3">
-        <f t="shared" ref="D3:D50" si="0">(F3-E3)/4</f>
+        <f t="shared" ref="D3:D53" si="0">(F3-E3)/4</f>
         <v>24.75</v>
       </c>
       <c r="E3">
@@ -1310,23 +1308,23 @@
         <v>25</v>
       </c>
       <c r="B26" t="s">
-        <v>39</v>
+        <v>78</v>
       </c>
       <c r="C26">
-        <v>0.8</v>
+        <v>40</v>
       </c>
       <c r="D26">
         <f t="shared" si="0"/>
-        <v>0.24975</v>
-      </c>
-      <c r="E26">
-        <v>1E-3</v>
+        <v>15</v>
+      </c>
+      <c r="E26" s="4">
+        <v>10</v>
       </c>
       <c r="F26">
-        <v>1</v>
+        <v>70</v>
       </c>
       <c r="G26">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="27" spans="1:8" x14ac:dyDescent="0.25">
@@ -1334,10 +1332,10 @@
         <v>26</v>
       </c>
       <c r="B27" t="s">
-        <v>40</v>
+        <v>39</v>
       </c>
       <c r="C27">
-        <v>1E-3</v>
+        <v>0.8</v>
       </c>
       <c r="D27">
         <f t="shared" si="0"/>
@@ -1358,20 +1356,20 @@
         <v>27</v>
       </c>
       <c r="B28" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="C28">
-        <v>0.5</v>
+        <v>1E-3</v>
       </c>
       <c r="D28">
         <f t="shared" si="0"/>
-        <v>2.4997500000000001</v>
+        <v>0.24975</v>
       </c>
       <c r="E28">
         <v>1E-3</v>
       </c>
       <c r="F28">
-        <v>10</v>
+        <v>1</v>
       </c>
       <c r="G28">
         <v>1</v>
@@ -1382,26 +1380,23 @@
         <v>28</v>
       </c>
       <c r="B29" t="s">
-        <v>42</v>
+        <v>41</v>
       </c>
       <c r="C29">
-        <v>0.7</v>
+        <v>0.5</v>
       </c>
       <c r="D29">
         <f t="shared" si="0"/>
-        <v>5.0000000000000017E-2</v>
-      </c>
-      <c r="E29" s="2">
-        <v>0.6</v>
-      </c>
-      <c r="F29" s="2">
-        <v>0.8</v>
+        <v>2.4997500000000001</v>
+      </c>
+      <c r="E29">
+        <v>1E-3</v>
+      </c>
+      <c r="F29">
+        <v>10</v>
       </c>
       <c r="G29">
-        <v>4</v>
-      </c>
-      <c r="H29" t="s">
-        <v>10</v>
+        <v>1</v>
       </c>
     </row>
     <row r="30" spans="1:8" x14ac:dyDescent="0.25">
@@ -1409,20 +1404,20 @@
         <v>29</v>
       </c>
       <c r="B30" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
       <c r="C30">
-        <v>0.5</v>
+        <v>0.7</v>
       </c>
       <c r="D30">
         <f t="shared" si="0"/>
-        <v>4.9999999999999989E-2</v>
+        <v>5.0000000000000017E-2</v>
       </c>
       <c r="E30" s="2">
-        <v>0.4</v>
+        <v>0.6</v>
       </c>
       <c r="F30" s="2">
-        <v>0.6</v>
+        <v>0.8</v>
       </c>
       <c r="G30">
         <v>4</v>
@@ -1436,23 +1431,23 @@
         <v>30</v>
       </c>
       <c r="B31" t="s">
-        <v>44</v>
+        <v>79</v>
       </c>
       <c r="C31">
-        <v>1E-3</v>
+        <v>20</v>
       </c>
       <c r="D31">
         <f t="shared" si="0"/>
-        <v>0.24975</v>
-      </c>
-      <c r="E31">
-        <v>1E-3</v>
-      </c>
-      <c r="F31">
-        <v>1</v>
+        <v>15</v>
+      </c>
+      <c r="E31" s="4">
+        <v>10</v>
+      </c>
+      <c r="F31" s="4">
+        <v>70</v>
       </c>
       <c r="G31">
-        <v>1</v>
+        <v>4</v>
       </c>
     </row>
     <row r="32" spans="1:8" x14ac:dyDescent="0.25">
@@ -1460,23 +1455,26 @@
         <v>31</v>
       </c>
       <c r="B32" t="s">
-        <v>45</v>
+        <v>43</v>
       </c>
       <c r="C32">
-        <v>48</v>
+        <v>0.5</v>
       </c>
       <c r="D32">
         <f t="shared" si="0"/>
-        <v>0.5</v>
+        <v>4.9999999999999989E-2</v>
       </c>
       <c r="E32" s="2">
-        <v>47</v>
+        <v>0.4</v>
       </c>
       <c r="F32" s="2">
-        <v>49</v>
+        <v>0.6</v>
       </c>
       <c r="G32">
         <v>4</v>
+      </c>
+      <c r="H32" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="33" spans="1:8" x14ac:dyDescent="0.25">
@@ -1484,20 +1482,20 @@
         <v>32</v>
       </c>
       <c r="B33" t="s">
-        <v>46</v>
+        <v>44</v>
       </c>
       <c r="C33">
-        <v>30.46</v>
+        <v>1E-3</v>
       </c>
       <c r="D33">
         <f t="shared" si="0"/>
-        <v>22.5</v>
-      </c>
-      <c r="E33" s="2">
-        <v>10</v>
-      </c>
-      <c r="F33" s="2">
-        <v>100</v>
+        <v>0.24975</v>
+      </c>
+      <c r="E33">
+        <v>1E-3</v>
+      </c>
+      <c r="F33">
+        <v>1</v>
       </c>
       <c r="G33">
         <v>1</v>
@@ -1508,23 +1506,26 @@
         <v>33</v>
       </c>
       <c r="B34" t="s">
+        <v>45</v>
+      </c>
+      <c r="C34">
+        <v>48</v>
+      </c>
+      <c r="D34">
+        <f t="shared" si="0"/>
+        <v>0.5</v>
+      </c>
+      <c r="E34" s="2">
         <v>47</v>
       </c>
-      <c r="C34">
-        <v>0.1</v>
-      </c>
-      <c r="D34">
-        <f t="shared" si="0"/>
-        <v>0.24975</v>
-      </c>
-      <c r="E34">
-        <v>1E-3</v>
-      </c>
-      <c r="F34">
-        <v>1</v>
+      <c r="F34" s="2">
+        <v>49</v>
       </c>
       <c r="G34">
-        <v>2</v>
+        <v>4</v>
+      </c>
+      <c r="H34" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="35" spans="1:8" x14ac:dyDescent="0.25">
@@ -1532,20 +1533,20 @@
         <v>34</v>
       </c>
       <c r="B35" t="s">
-        <v>48</v>
+        <v>46</v>
       </c>
       <c r="C35">
-        <v>0.11</v>
+        <v>30.46</v>
       </c>
       <c r="D35">
         <f t="shared" si="0"/>
-        <v>0.27225000000000005</v>
+        <v>22.5</v>
       </c>
       <c r="E35" s="2">
-        <v>1.0999999999999999E-2</v>
+        <v>10</v>
       </c>
       <c r="F35" s="2">
-        <v>1.1000000000000001</v>
+        <v>100</v>
       </c>
       <c r="G35">
         <v>1</v>
@@ -1559,26 +1560,23 @@
         <v>35</v>
       </c>
       <c r="B36" t="s">
-        <v>49</v>
+        <v>47</v>
       </c>
       <c r="C36">
-        <v>0.83</v>
+        <v>0.1</v>
       </c>
       <c r="D36">
         <f t="shared" si="0"/>
-        <v>2.0542500000000001</v>
-      </c>
-      <c r="E36" s="2">
-        <v>8.3000000000000004E-2</v>
-      </c>
-      <c r="F36" s="2">
-        <v>8.3000000000000007</v>
+        <v>0.24975</v>
+      </c>
+      <c r="E36">
+        <v>1E-3</v>
+      </c>
+      <c r="F36">
+        <v>1</v>
       </c>
       <c r="G36">
-        <v>1</v>
-      </c>
-      <c r="H36" t="s">
-        <v>10</v>
+        <v>2</v>
       </c>
     </row>
     <row r="37" spans="1:8" x14ac:dyDescent="0.25">
@@ -1586,23 +1584,26 @@
         <v>36</v>
       </c>
       <c r="B37" t="s">
-        <v>50</v>
+        <v>48</v>
       </c>
       <c r="C37">
-        <v>1</v>
+        <v>0.11</v>
       </c>
       <c r="D37">
         <f t="shared" si="0"/>
-        <v>2.25</v>
-      </c>
-      <c r="E37">
-        <v>1</v>
-      </c>
-      <c r="F37">
-        <v>10</v>
+        <v>0.27225000000000005</v>
+      </c>
+      <c r="E37" s="2">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="F37" s="2">
+        <v>1.1000000000000001</v>
       </c>
       <c r="G37">
         <v>1</v>
+      </c>
+      <c r="H37" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="38" spans="1:8" x14ac:dyDescent="0.25">
@@ -1610,23 +1611,26 @@
         <v>37</v>
       </c>
       <c r="B38" t="s">
-        <v>51</v>
+        <v>49</v>
       </c>
       <c r="C38">
-        <v>2.58</v>
+        <v>0.83</v>
       </c>
       <c r="D38">
         <f t="shared" si="0"/>
-        <v>2.25</v>
-      </c>
-      <c r="E38">
-        <v>1</v>
-      </c>
-      <c r="F38">
-        <v>10</v>
+        <v>2.0542500000000001</v>
+      </c>
+      <c r="E38" s="2">
+        <v>8.3000000000000004E-2</v>
+      </c>
+      <c r="F38" s="2">
+        <v>8.3000000000000007</v>
       </c>
       <c r="G38">
         <v>1</v>
+      </c>
+      <c r="H38" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="39" spans="1:8" x14ac:dyDescent="0.25">
@@ -1634,26 +1638,23 @@
         <v>38</v>
       </c>
       <c r="B39" t="s">
-        <v>52</v>
+        <v>50</v>
       </c>
       <c r="C39">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c r="D39">
         <f t="shared" si="0"/>
-        <v>0</v>
-      </c>
-      <c r="E39" s="2">
-        <v>0</v>
-      </c>
-      <c r="F39" s="2">
-        <v>0</v>
+        <v>2.25</v>
+      </c>
+      <c r="E39">
+        <v>1</v>
+      </c>
+      <c r="F39">
+        <v>10</v>
       </c>
       <c r="G39">
         <v>1</v>
-      </c>
-      <c r="H39" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="40" spans="1:8" x14ac:dyDescent="0.25">
@@ -1661,10 +1662,10 @@
         <v>39</v>
       </c>
       <c r="B40" t="s">
-        <v>53</v>
+        <v>51</v>
       </c>
       <c r="C40">
-        <v>1</v>
+        <v>2.58</v>
       </c>
       <c r="D40">
         <f t="shared" si="0"/>
@@ -1685,23 +1686,26 @@
         <v>40</v>
       </c>
       <c r="B41" t="s">
-        <v>54</v>
+        <v>52</v>
       </c>
       <c r="C41">
-        <v>15.31</v>
+        <v>0</v>
       </c>
       <c r="D41">
         <f t="shared" si="0"/>
-        <v>10</v>
-      </c>
-      <c r="E41">
-        <v>10</v>
-      </c>
-      <c r="F41">
-        <v>50</v>
+        <v>0</v>
+      </c>
+      <c r="E41" s="2">
+        <v>0</v>
+      </c>
+      <c r="F41" s="2">
+        <v>0</v>
       </c>
       <c r="G41">
         <v>1</v>
+      </c>
+      <c r="H41" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="42" spans="1:8" x14ac:dyDescent="0.25">
@@ -1709,10 +1713,10 @@
         <v>41</v>
       </c>
       <c r="B42" t="s">
-        <v>55</v>
+        <v>53</v>
       </c>
       <c r="C42">
-        <v>5</v>
+        <v>1</v>
       </c>
       <c r="D42">
         <f t="shared" si="0"/>
@@ -1725,7 +1729,7 @@
         <v>10</v>
       </c>
       <c r="G42">
-        <v>2</v>
+        <v>1</v>
       </c>
     </row>
     <row r="43" spans="1:8" x14ac:dyDescent="0.25">
@@ -1733,26 +1737,23 @@
         <v>42</v>
       </c>
       <c r="B43" t="s">
-        <v>56</v>
+        <v>80</v>
       </c>
       <c r="C43">
-        <v>0.11</v>
+        <v>20</v>
       </c>
       <c r="D43">
-        <f t="shared" ref="D43" si="1">(F43-E43)/4</f>
-        <v>0.27225000000000005</v>
-      </c>
-      <c r="E43" s="2">
-        <v>1.0999999999999999E-2</v>
-      </c>
-      <c r="F43" s="2">
-        <v>1.1000000000000001</v>
+        <f t="shared" si="0"/>
+        <v>15</v>
+      </c>
+      <c r="E43">
+        <v>10</v>
+      </c>
+      <c r="F43">
+        <v>70</v>
       </c>
       <c r="G43">
-        <v>1</v>
-      </c>
-      <c r="H43" t="s">
-        <v>10</v>
+        <v>4</v>
       </c>
     </row>
     <row r="44" spans="1:8" x14ac:dyDescent="0.25">
@@ -1760,20 +1761,20 @@
         <v>43</v>
       </c>
       <c r="B44" t="s">
-        <v>57</v>
+        <v>54</v>
       </c>
       <c r="C44">
-        <v>1.3</v>
+        <v>15.31</v>
       </c>
       <c r="D44">
-        <f>(F44-E44)/4</f>
-        <v>3.2174999999999998</v>
-      </c>
-      <c r="E44" s="2">
-        <v>0.13</v>
-      </c>
-      <c r="F44" s="2">
-        <v>13</v>
+        <f t="shared" si="0"/>
+        <v>10</v>
+      </c>
+      <c r="E44">
+        <v>10</v>
+      </c>
+      <c r="F44">
+        <v>50</v>
       </c>
       <c r="G44">
         <v>1</v>
@@ -1787,23 +1788,23 @@
         <v>44</v>
       </c>
       <c r="B45" t="s">
-        <v>58</v>
-      </c>
-      <c r="C45" s="1">
-        <v>10</v>
+        <v>55</v>
+      </c>
+      <c r="C45">
+        <v>5</v>
       </c>
       <c r="D45">
         <f t="shared" si="0"/>
-        <v>24.75</v>
+        <v>2.25</v>
       </c>
       <c r="E45">
         <v>1</v>
       </c>
       <c r="F45">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="G45">
-        <v>1</v>
+        <v>2</v>
       </c>
     </row>
     <row r="46" spans="1:8" x14ac:dyDescent="0.25">
@@ -1811,23 +1812,26 @@
         <v>45</v>
       </c>
       <c r="B46" t="s">
-        <v>59</v>
-      </c>
-      <c r="C46" s="1">
-        <v>6.45</v>
+        <v>56</v>
+      </c>
+      <c r="C46">
+        <v>0.11</v>
       </c>
       <c r="D46">
-        <f t="shared" si="0"/>
-        <v>15.963749999999999</v>
-      </c>
-      <c r="E46">
-        <v>0.64500000000000002</v>
-      </c>
-      <c r="F46">
-        <v>64.5</v>
+        <f t="shared" ref="D46" si="1">(F46-E46)/4</f>
+        <v>0.27225000000000005</v>
+      </c>
+      <c r="E46" s="2">
+        <v>1.0999999999999999E-2</v>
+      </c>
+      <c r="F46" s="2">
+        <v>1.1000000000000001</v>
       </c>
       <c r="G46">
         <v>1</v>
+      </c>
+      <c r="H46" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="47" spans="1:8" x14ac:dyDescent="0.25">
@@ -1835,23 +1839,26 @@
         <v>46</v>
       </c>
       <c r="B47" t="s">
-        <v>60</v>
-      </c>
-      <c r="C47" s="1">
-        <v>3.6</v>
+        <v>57</v>
+      </c>
+      <c r="C47">
+        <v>1.3</v>
       </c>
       <c r="D47">
-        <f t="shared" si="0"/>
-        <v>8.91</v>
-      </c>
-      <c r="E47">
-        <v>0.36</v>
-      </c>
-      <c r="F47">
-        <v>36</v>
+        <f>(F47-E47)/4</f>
+        <v>3.2174999999999998</v>
+      </c>
+      <c r="E47" s="2">
+        <v>0.13</v>
+      </c>
+      <c r="F47" s="2">
+        <v>13</v>
       </c>
       <c r="G47">
         <v>1</v>
+      </c>
+      <c r="H47" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="48" spans="1:8" x14ac:dyDescent="0.25">
@@ -1859,20 +1866,20 @@
         <v>47</v>
       </c>
       <c r="B48" t="s">
-        <v>61</v>
+        <v>58</v>
       </c>
       <c r="C48" s="1">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="D48">
         <f t="shared" si="0"/>
-        <v>49.5</v>
+        <v>24.75</v>
       </c>
       <c r="E48">
-        <v>2</v>
+        <v>1</v>
       </c>
       <c r="F48">
-        <v>200</v>
+        <v>100</v>
       </c>
       <c r="G48">
         <v>1</v>
@@ -1883,20 +1890,20 @@
         <v>48</v>
       </c>
       <c r="B49" t="s">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="C49" s="1">
-        <v>38</v>
+        <v>6.45</v>
       </c>
       <c r="D49">
         <f t="shared" si="0"/>
-        <v>94.05</v>
+        <v>15.963749999999999</v>
       </c>
       <c r="E49">
-        <v>3.8</v>
+        <v>0.64500000000000002</v>
       </c>
       <c r="F49">
-        <v>380</v>
+        <v>64.5</v>
       </c>
       <c r="G49">
         <v>1</v>
@@ -1907,20 +1914,20 @@
         <v>49</v>
       </c>
       <c r="B50" t="s">
-        <v>63</v>
+        <v>60</v>
       </c>
       <c r="C50" s="1">
-        <v>16.600000000000001</v>
+        <v>3.6</v>
       </c>
       <c r="D50">
         <f t="shared" si="0"/>
-        <v>41.085000000000001</v>
+        <v>8.91</v>
       </c>
       <c r="E50">
-        <v>1.66</v>
+        <v>0.36</v>
       </c>
       <c r="F50">
-        <v>166</v>
+        <v>36</v>
       </c>
       <c r="G50">
         <v>1</v>
@@ -1931,31 +1938,23 @@
         <v>50</v>
       </c>
       <c r="B51" t="s">
-        <v>64</v>
-      </c>
-      <c r="C51">
-        <v>125</v>
+        <v>61</v>
+      </c>
+      <c r="C51" s="1">
+        <v>20</v>
       </c>
       <c r="D51">
-        <f t="shared" ref="D51:D68" si="2">(F51-E51)/4</f>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>49.5</v>
       </c>
       <c r="E51">
-        <f>C51</f>
-        <v>125</v>
+        <v>2</v>
       </c>
       <c r="F51">
-        <f>C51</f>
-        <v>125</v>
+        <v>200</v>
       </c>
       <c r="G51">
         <v>1</v>
-      </c>
-      <c r="H51" t="s">
-        <v>10</v>
-      </c>
-      <c r="J51" t="s">
-        <v>7</v>
       </c>
     </row>
     <row r="52" spans="1:10" x14ac:dyDescent="0.25">
@@ -1963,28 +1962,23 @@
         <v>51</v>
       </c>
       <c r="B52" t="s">
-        <v>65</v>
-      </c>
-      <c r="C52">
-        <v>58</v>
+        <v>62</v>
+      </c>
+      <c r="C52" s="1">
+        <v>38</v>
       </c>
       <c r="D52">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>94.05</v>
       </c>
       <c r="E52">
-        <f t="shared" ref="E52:E68" si="3">C52</f>
-        <v>58</v>
+        <v>3.8</v>
       </c>
       <c r="F52">
-        <f t="shared" ref="F52:F68" si="4">C52</f>
-        <v>58</v>
+        <v>380</v>
       </c>
       <c r="G52">
         <v>1</v>
-      </c>
-      <c r="H52" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="53" spans="1:10" x14ac:dyDescent="0.25">
@@ -1992,28 +1986,23 @@
         <v>52</v>
       </c>
       <c r="B53" t="s">
-        <v>66</v>
-      </c>
-      <c r="C53">
-        <v>971</v>
+        <v>63</v>
+      </c>
+      <c r="C53" s="1">
+        <v>16.600000000000001</v>
       </c>
       <c r="D53">
-        <f t="shared" si="2"/>
-        <v>0</v>
+        <f t="shared" si="0"/>
+        <v>41.085000000000001</v>
       </c>
       <c r="E53">
-        <f t="shared" si="3"/>
-        <v>971</v>
+        <v>1.66</v>
       </c>
       <c r="F53">
-        <f t="shared" si="4"/>
-        <v>971</v>
+        <v>166</v>
       </c>
       <c r="G53">
         <v>1</v>
-      </c>
-      <c r="H53" t="s">
-        <v>10</v>
       </c>
     </row>
     <row r="54" spans="1:10" x14ac:dyDescent="0.25">
@@ -2021,28 +2010,31 @@
         <v>53</v>
       </c>
       <c r="B54" t="s">
-        <v>67</v>
+        <v>64</v>
       </c>
       <c r="C54">
-        <v>1.0369999999999999</v>
+        <v>-1.619</v>
       </c>
       <c r="D54">
-        <f t="shared" si="2"/>
+        <f t="shared" ref="D54:D67" si="2">(F54-E54)/4</f>
         <v>0</v>
       </c>
       <c r="E54">
-        <f t="shared" si="3"/>
-        <v>1.0369999999999999</v>
+        <f>C54</f>
+        <v>-1.619</v>
       </c>
       <c r="F54">
-        <f t="shared" si="4"/>
-        <v>1.0369999999999999</v>
+        <f>C54</f>
+        <v>-1.619</v>
       </c>
       <c r="G54">
         <v>1</v>
       </c>
       <c r="H54" t="s">
         <v>10</v>
+      </c>
+      <c r="J54" t="s">
+        <v>7</v>
       </c>
     </row>
     <row r="55" spans="1:10" x14ac:dyDescent="0.25">
@@ -2050,22 +2042,22 @@
         <v>54</v>
       </c>
       <c r="B55" t="s">
-        <v>68</v>
+        <v>65</v>
       </c>
       <c r="C55">
-        <v>756</v>
+        <v>8592</v>
       </c>
       <c r="D55">
         <f t="shared" si="2"/>
         <v>0</v>
       </c>
       <c r="E55">
-        <f t="shared" si="3"/>
-        <v>756</v>
+        <f t="shared" ref="E55:E67" si="3">C55</f>
+        <v>8592</v>
       </c>
       <c r="F55">
-        <f t="shared" si="4"/>
-        <v>756</v>
+        <f t="shared" ref="F55:F67" si="4">C55</f>
+        <v>8592</v>
       </c>
       <c r="G55">
         <v>1</v>
@@ -2079,10 +2071,10 @@
         <v>55</v>
       </c>
       <c r="B56" t="s">
-        <v>69</v>
+        <v>77</v>
       </c>
       <c r="C56">
-        <v>0.51600000000000001</v>
+        <v>1.5E-3</v>
       </c>
       <c r="D56">
         <f t="shared" si="2"/>
@@ -2090,11 +2082,11 @@
       </c>
       <c r="E56">
         <f t="shared" si="3"/>
-        <v>0.51600000000000001</v>
+        <v>1.5E-3</v>
       </c>
       <c r="F56">
         <f t="shared" si="4"/>
-        <v>0.51600000000000001</v>
+        <v>1.5E-3</v>
       </c>
       <c r="G56">
         <v>1</v>
@@ -2108,10 +2100,10 @@
         <v>56</v>
       </c>
       <c r="B57" t="s">
-        <v>70</v>
+        <v>66</v>
       </c>
       <c r="C57">
-        <v>0.16500000000000001</v>
+        <v>1769.8</v>
       </c>
       <c r="D57">
         <f t="shared" si="2"/>
@@ -2119,11 +2111,11 @@
       </c>
       <c r="E57">
         <f t="shared" si="3"/>
-        <v>0.16500000000000001</v>
+        <v>1769.8</v>
       </c>
       <c r="F57">
         <f t="shared" si="4"/>
-        <v>0.16500000000000001</v>
+        <v>1769.8</v>
       </c>
       <c r="G57">
         <v>1</v>
@@ -2137,10 +2129,10 @@
         <v>57</v>
       </c>
       <c r="B58" t="s">
-        <v>71</v>
+        <v>67</v>
       </c>
       <c r="C58">
-        <v>1769.8</v>
+        <v>258.5</v>
       </c>
       <c r="D58">
         <f t="shared" si="2"/>
@@ -2148,11 +2140,11 @@
       </c>
       <c r="E58">
         <f t="shared" si="3"/>
-        <v>1769.8</v>
+        <v>258.5</v>
       </c>
       <c r="F58">
         <f t="shared" si="4"/>
-        <v>1769.8</v>
+        <v>258.5</v>
       </c>
       <c r="G58">
         <v>1</v>
@@ -2166,10 +2158,10 @@
         <v>58</v>
       </c>
       <c r="B59" t="s">
-        <v>72</v>
+        <v>68</v>
       </c>
       <c r="C59">
-        <v>258.5</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="D59">
         <f t="shared" si="2"/>
@@ -2177,11 +2169,11 @@
       </c>
       <c r="E59">
         <f t="shared" si="3"/>
-        <v>258.5</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="F59">
         <f t="shared" si="4"/>
-        <v>258.5</v>
+        <v>0.23400000000000001</v>
       </c>
       <c r="G59">
         <v>1</v>
@@ -2195,10 +2187,10 @@
         <v>59</v>
       </c>
       <c r="B60" t="s">
-        <v>73</v>
+        <v>69</v>
       </c>
       <c r="C60">
-        <v>0.23400000000000001</v>
+        <v>7.7850000000000001</v>
       </c>
       <c r="D60">
         <f t="shared" si="2"/>
@@ -2206,11 +2198,11 @@
       </c>
       <c r="E60">
         <f t="shared" si="3"/>
-        <v>0.23400000000000001</v>
+        <v>7.7850000000000001</v>
       </c>
       <c r="F60">
         <f t="shared" si="4"/>
-        <v>0.23400000000000001</v>
+        <v>7.7850000000000001</v>
       </c>
       <c r="G60">
         <v>1</v>
@@ -2224,10 +2216,10 @@
         <v>60</v>
       </c>
       <c r="B61" t="s">
-        <v>74</v>
+        <v>70</v>
       </c>
       <c r="C61">
-        <v>7.7850000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="D61">
         <f t="shared" si="2"/>
@@ -2235,11 +2227,11 @@
       </c>
       <c r="E61">
         <f t="shared" si="3"/>
-        <v>7.7850000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="F61">
         <f t="shared" si="4"/>
-        <v>7.7850000000000001</v>
+        <v>0.15</v>
       </c>
       <c r="G61">
         <v>1</v>
@@ -2253,10 +2245,10 @@
         <v>61</v>
       </c>
       <c r="B62" t="s">
-        <v>75</v>
+        <v>71</v>
       </c>
       <c r="C62">
-        <v>0.15</v>
+        <v>1.36</v>
       </c>
       <c r="D62">
         <f t="shared" si="2"/>
@@ -2264,11 +2256,11 @@
       </c>
       <c r="E62">
         <f t="shared" si="3"/>
-        <v>0.15</v>
+        <v>1.36</v>
       </c>
       <c r="F62">
         <f t="shared" si="4"/>
-        <v>0.15</v>
+        <v>1.36</v>
       </c>
       <c r="G62">
         <v>1</v>
@@ -2282,10 +2274,10 @@
         <v>62</v>
       </c>
       <c r="B63" t="s">
-        <v>76</v>
+        <v>72</v>
       </c>
       <c r="C63">
-        <v>1.36</v>
+        <v>72.477999999999994</v>
       </c>
       <c r="D63">
         <f t="shared" si="2"/>
@@ -2293,11 +2285,11 @@
       </c>
       <c r="E63">
         <f t="shared" si="3"/>
-        <v>1.36</v>
+        <v>72.477999999999994</v>
       </c>
       <c r="F63">
         <f t="shared" si="4"/>
-        <v>1.36</v>
+        <v>72.477999999999994</v>
       </c>
       <c r="G63">
         <v>1</v>
@@ -2311,10 +2303,10 @@
         <v>63</v>
       </c>
       <c r="B64" t="s">
-        <v>77</v>
+        <v>73</v>
       </c>
       <c r="C64">
-        <v>72.477999999999994</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="D64">
         <f t="shared" si="2"/>
@@ -2322,11 +2314,11 @@
       </c>
       <c r="E64">
         <f t="shared" si="3"/>
-        <v>72.477999999999994</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="F64">
         <f t="shared" si="4"/>
-        <v>72.477999999999994</v>
+        <v>0.13100000000000001</v>
       </c>
       <c r="G64">
         <v>1</v>
@@ -2340,10 +2332,10 @@
         <v>64</v>
       </c>
       <c r="B65" t="s">
-        <v>78</v>
+        <v>74</v>
       </c>
       <c r="C65">
-        <v>0.13100000000000001</v>
+        <v>22.033999999999999</v>
       </c>
       <c r="D65">
         <f t="shared" si="2"/>
@@ -2351,11 +2343,11 @@
       </c>
       <c r="E65">
         <f t="shared" si="3"/>
-        <v>0.13100000000000001</v>
+        <v>22.033999999999999</v>
       </c>
       <c r="F65">
         <f t="shared" si="4"/>
-        <v>0.13100000000000001</v>
+        <v>22.033999999999999</v>
       </c>
       <c r="G65">
         <v>1</v>
@@ -2369,10 +2361,10 @@
         <v>65</v>
       </c>
       <c r="B66" t="s">
-        <v>79</v>
+        <v>75</v>
       </c>
       <c r="C66">
-        <v>22.033999999999999</v>
+        <v>3.2839999999999998</v>
       </c>
       <c r="D66">
         <f t="shared" si="2"/>
@@ -2380,11 +2372,11 @@
       </c>
       <c r="E66">
         <f t="shared" si="3"/>
-        <v>22.033999999999999</v>
+        <v>3.2839999999999998</v>
       </c>
       <c r="F66">
         <f t="shared" si="4"/>
-        <v>22.033999999999999</v>
+        <v>3.2839999999999998</v>
       </c>
       <c r="G66">
         <v>1</v>
@@ -2398,10 +2390,10 @@
         <v>66</v>
       </c>
       <c r="B67" t="s">
-        <v>80</v>
+        <v>76</v>
       </c>
       <c r="C67">
-        <v>3.2839999999999998</v>
+        <v>35.752000000000002</v>
       </c>
       <c r="D67">
         <f t="shared" si="2"/>
@@ -2409,45 +2401,16 @@
       </c>
       <c r="E67">
         <f t="shared" si="3"/>
-        <v>3.2839999999999998</v>
+        <v>35.752000000000002</v>
       </c>
       <c r="F67">
         <f t="shared" si="4"/>
-        <v>3.2839999999999998</v>
+        <v>35.752000000000002</v>
       </c>
       <c r="G67">
         <v>1</v>
       </c>
       <c r="H67" t="s">
-        <v>10</v>
-      </c>
-    </row>
-    <row r="68" spans="1:8" x14ac:dyDescent="0.25">
-      <c r="A68">
-        <v>67</v>
-      </c>
-      <c r="B68" t="s">
-        <v>81</v>
-      </c>
-      <c r="C68">
-        <v>35.752000000000002</v>
-      </c>
-      <c r="D68">
-        <f t="shared" si="2"/>
-        <v>0</v>
-      </c>
-      <c r="E68">
-        <f t="shared" si="3"/>
-        <v>35.752000000000002</v>
-      </c>
-      <c r="F68">
-        <f t="shared" si="4"/>
-        <v>35.752000000000002</v>
-      </c>
-      <c r="G68">
-        <v>1</v>
-      </c>
-      <c r="H68" t="s">
         <v>10</v>
       </c>
     </row>

--- a/parameters.xlsx
+++ b/parameters.xlsx
@@ -5,12 +5,12 @@
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\mmunip.CAMPUS\source\repos\ABM-NM-optimization\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\megmu\source\repos\megmuni\ABM-Random-Forest\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{1C141CB2-284A-4BA7-9291-C48AA37AE700}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{A21C1746-17A8-45AC-99F2-6D813D109ABD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="6075" yWindow="2325" windowWidth="21600" windowHeight="11295" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -325,12 +325,11 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="5">
+  <cellXfs count="4">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="0" fillId="2" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="0" fillId="3" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="11" fontId="0" fillId="3" borderId="0" xfId="0" applyNumberFormat="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -646,14 +645,14 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:K67"/>
-  <sheetFormatPr defaultColWidth="8.85546875" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="2" width="21" customWidth="1"/>
-    <col min="3" max="3" width="22.140625" customWidth="1"/>
+    <col min="3" max="3" width="22.109375" customWidth="1"/>
     <col min="4" max="4" width="22" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>13</v>
       </c>
@@ -679,7 +678,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="2" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
@@ -709,7 +708,7 @@
         <v>3</v>
       </c>
     </row>
-    <row r="3" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
@@ -739,7 +738,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="4" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
@@ -769,7 +768,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
@@ -799,7 +798,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="6" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
@@ -829,7 +828,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
@@ -853,7 +852,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="8" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
@@ -877,7 +876,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="9" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
@@ -901,7 +900,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="10" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
@@ -925,7 +924,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="11" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
@@ -949,7 +948,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="12" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12">
         <v>11</v>
       </c>
@@ -973,7 +972,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="13" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A13">
         <v>12</v>
       </c>
@@ -997,7 +996,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="14" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A14">
         <v>13</v>
       </c>
@@ -1021,7 +1020,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="15" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="15" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A15">
         <v>14</v>
       </c>
@@ -1045,7 +1044,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="16" spans="1:11" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A16">
         <v>15</v>
       </c>
@@ -1072,7 +1071,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17">
         <v>16</v>
       </c>
@@ -1096,7 +1095,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18">
         <v>17</v>
       </c>
@@ -1123,7 +1122,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19">
         <v>18</v>
       </c>
@@ -1150,7 +1149,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20">
         <v>19</v>
       </c>
@@ -1162,10 +1161,10 @@
       </c>
       <c r="D20">
         <f t="shared" si="0"/>
-        <v>2.25</v>
+        <v>2.4975000000000001</v>
       </c>
       <c r="E20">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="F20">
         <v>10</v>
@@ -1174,7 +1173,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21">
         <v>20</v>
       </c>
@@ -1201,7 +1200,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22">
         <v>21</v>
       </c>
@@ -1228,7 +1227,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="23" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A23">
         <v>22</v>
       </c>
@@ -1252,7 +1251,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A24">
         <v>23</v>
       </c>
@@ -1279,7 +1278,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A25">
         <v>24</v>
       </c>
@@ -1303,7 +1302,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A26">
         <v>25</v>
       </c>
@@ -1317,7 +1316,7 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="E26" s="4">
+      <c r="E26">
         <v>10</v>
       </c>
       <c r="F26">
@@ -1327,7 +1326,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A27">
         <v>26</v>
       </c>
@@ -1351,7 +1350,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A28">
         <v>27</v>
       </c>
@@ -1375,7 +1374,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A29">
         <v>28</v>
       </c>
@@ -1399,7 +1398,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A30">
         <v>29</v>
       </c>
@@ -1426,7 +1425,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A31">
         <v>30</v>
       </c>
@@ -1440,17 +1439,17 @@
         <f t="shared" si="0"/>
         <v>15</v>
       </c>
-      <c r="E31" s="4">
-        <v>10</v>
-      </c>
-      <c r="F31" s="4">
+      <c r="E31">
+        <v>10</v>
+      </c>
+      <c r="F31">
         <v>70</v>
       </c>
       <c r="G31">
         <v>4</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A32">
         <v>31</v>
       </c>
@@ -1477,7 +1476,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A33">
         <v>32</v>
       </c>
@@ -1501,7 +1500,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A34">
         <v>33</v>
       </c>
@@ -1528,7 +1527,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A35">
         <v>34</v>
       </c>
@@ -1555,7 +1554,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A36">
         <v>35</v>
       </c>
@@ -1579,7 +1578,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A37">
         <v>36</v>
       </c>
@@ -1606,7 +1605,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A38">
         <v>37</v>
       </c>
@@ -1633,7 +1632,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A39">
         <v>38</v>
       </c>
@@ -1645,10 +1644,10 @@
       </c>
       <c r="D39">
         <f t="shared" si="0"/>
-        <v>2.25</v>
+        <v>2.4975000000000001</v>
       </c>
       <c r="E39">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="F39">
         <v>10</v>
@@ -1657,7 +1656,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A40">
         <v>39</v>
       </c>
@@ -1669,10 +1668,10 @@
       </c>
       <c r="D40">
         <f t="shared" si="0"/>
-        <v>2.25</v>
+        <v>2.4975000000000001</v>
       </c>
       <c r="E40">
-        <v>1</v>
+        <v>0.01</v>
       </c>
       <c r="F40">
         <v>10</v>
@@ -1681,7 +1680,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A41">
         <v>40</v>
       </c>
@@ -1708,7 +1707,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A42">
         <v>41</v>
       </c>
@@ -1732,7 +1731,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A43">
         <v>42</v>
       </c>
@@ -1756,7 +1755,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A44">
         <v>43</v>
       </c>
@@ -1783,7 +1782,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A45">
         <v>44</v>
       </c>
@@ -1807,7 +1806,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A46">
         <v>45</v>
       </c>
@@ -1834,7 +1833,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A47">
         <v>46</v>
       </c>
@@ -1861,7 +1860,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A48">
         <v>47</v>
       </c>
@@ -1885,7 +1884,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="49" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="49" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A49">
         <v>48</v>
       </c>
@@ -1909,7 +1908,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="50" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="50" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A50">
         <v>49</v>
       </c>
@@ -1933,7 +1932,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="51" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="51" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A51">
         <v>50</v>
       </c>
@@ -1957,7 +1956,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="52" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="52" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A52">
         <v>51</v>
       </c>
@@ -1981,7 +1980,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="53" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="53" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A53">
         <v>52</v>
       </c>
@@ -2005,7 +2004,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="54" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="54" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A54">
         <v>53</v>
       </c>
@@ -2037,7 +2036,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="55" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="55" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A55">
         <v>54</v>
       </c>
@@ -2066,7 +2065,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="56" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="56" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A56">
         <v>55</v>
       </c>
@@ -2095,7 +2094,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="57" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="57" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A57">
         <v>56</v>
       </c>
@@ -2124,7 +2123,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="58" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="58" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A58">
         <v>57</v>
       </c>
@@ -2153,7 +2152,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="59" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="59" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A59">
         <v>58</v>
       </c>
@@ -2182,7 +2181,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="60" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="60" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A60">
         <v>59</v>
       </c>
@@ -2211,7 +2210,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="61" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="61" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A61">
         <v>60</v>
       </c>
@@ -2240,7 +2239,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="62" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="62" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A62">
         <v>61</v>
       </c>
@@ -2269,7 +2268,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="63" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="63" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A63">
         <v>62</v>
       </c>
@@ -2298,7 +2297,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="64" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="64" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A64">
         <v>63</v>
       </c>
@@ -2327,7 +2326,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="65" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A65">
         <v>64</v>
       </c>
@@ -2356,7 +2355,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="66" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A66">
         <v>65</v>
       </c>
@@ -2385,7 +2384,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="67" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A67">
         <v>66</v>
       </c>
